--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,54 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R913707</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:53:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R921472</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-13 12:32:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R921482</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-13 12:38:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R924315</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-13 14:31:35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,18 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R933979</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:14:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>Fecha</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Stock Fantasma</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +444,9 @@
           <t>2026-07-13 10:12:23</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>0.42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +459,9 @@
           <t>2026-07-13 10:12:35</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +474,9 @@
           <t>2026-07-13 10:13:23</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,6 +489,9 @@
           <t>2026-07-13 10:15:34</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,6 +504,9 @@
           <t>2026-07-13 11:53:17</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +519,9 @@
           <t>2026-07-13 12:32:57</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -511,6 +534,9 @@
           <t>2026-07-13 12:38:30</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +549,9 @@
           <t>2026-07-13 14:31:35</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -534,6 +563,24 @@
         <is>
           <t>2026-07-13 16:14:14</t>
         </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R937805</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:36:37</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,10 +424,15 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Stock Fantasma</t>
         </is>
@@ -441,10 +446,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>FILTRO PAÑO LAVABLE  X MT2   RE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>2026-07-13 10:12:23</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -456,10 +466,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Termost.RANCO K59L1132  ARB420 27053 hel</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>2026-07-13 10:12:35</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -471,10 +486,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Termost.RANCO K59L2698 1.05 MTS SE REEMPLA R816606</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>2026-07-13 10:13:23</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -486,10 +506,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-13 10:15:34</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -501,10 +526,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>TAPA FUGAS ACH ANTON JERINGA X6ML</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>2026-07-13 11:53:17</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>13</v>
       </c>
     </row>
@@ -516,10 +546,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-13 12:32:57</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+          <t>SEP. ACEITE "BLUE STAR"XFB5303 7/8 DESARMABLE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEP. ACEITE "BLUE STAR"XFB5303 7/8 DESARMABLE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -531,10 +566,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-13 12:38:30</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -546,10 +586,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-13 14:31:35</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+          <t>FUNDENTE BLUESTAR FLUX-115gr.-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FUNDENTE BLUESTAR FLUX-115gr.-</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -561,10 +606,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>FORZADOR 13 VOLTS 3,3 WHATS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>2026-07-13 16:14:14</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -576,11 +626,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>PALA U. COND. DIAM. 40CM 3 ASPAS BUJE 8MM IZQ.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>2026-07-13 16:36:37</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R920759</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="66.140625" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -461,37 +464,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R816602</t>
+          <t>R816603</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Termost.RANCO K59L1132  ARB420 27053 hel</t>
+          <t>Termost.RANCO K59L2698 1.05 MTS SE REEMPLA R816606</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-13 10:12:35</t>
+          <t>2026-07-13 10:13:23</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R816603</t>
+          <t>R907058</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Termost.RANCO K59L2698 1.05 MTS SE REEMPLA R816606</t>
+          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-13 10:13:23</t>
+          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -501,97 +504,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R907058</t>
+          <t>R921482</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
+          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
+          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R913707</t>
+          <t>R937805</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TAPA FUGAS ACH ANTON JERINGA X6ML</t>
+          <t>PALA U. COND. DIAM. 40CM 3 ASPAS BUJE 8MM IZQ.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-13 11:53:17</t>
+          <t>2026-07-13 16:36:37</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R921472</t>
+          <t>R920759</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SEP. ACEITE "BLUE STAR"XFB5303 7/8 DESARMABLE</t>
+          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SEP. ACEITE "BLUE STAR"XFB5303 7/8 DESARMABLE</t>
+          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R921482</t>
+          <t>R955527</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
+          <t>Termost.RANCO K54L1819  27052 freez WHIR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
+          <t>2026-07-14 15:38:02</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R924315</t>
+          <t>R965930</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FUNDENTE BLUESTAR FLUX-115gr.-</t>
+          <t>KIT DE LLAVES ALLEN LARGO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FUNDENTE BLUESTAR FLUX-115gr.-</t>
+          <t>2026-07-15 09:28:38</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -601,17 +604,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R933979</t>
+          <t>R986608</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FORZADOR 13 VOLTS 3,3 WHATS</t>
+          <t>Presost.BlueStar HLP530M-Alta 8/30KgManu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-13 16:14:14</t>
+          <t>Presost.BlueStar HLP530M-Alta 8/30KgManu</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -621,41 +624,121 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R937805</t>
+          <t>R105842</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PALA U. COND. DIAM. 40CM 3 ASPAS BUJE 8MM IZQ.</t>
+          <t>JUEGO DE SUSPENSION COMPLETO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-13 16:36:37</t>
+          <t>2026-07-15 12:04:04</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R920759</t>
+          <t>R119279</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
+          <t>PLAQUETA WHIRPOOL WRE51D1/X1 WRX51D1/X1 326067825</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
+          <t>PLAQUETA WHIRPOOL WRE51D1/X1 WRX51D1/X1 326067825</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R119278</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PLAQUETA WHIRPOOL  W10314617  W10165343</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:36:12</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R119364</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PLACA REEMPLAZO WH W10165343 / 326053851</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PLACA REEMPLAZO WH W10165343 / 326053851</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R119365</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PLACA REEMPLAZO WH 326008614</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:46:43</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R119366</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PLACA REEMPLAZO WH 326005413</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:46:54</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -741,6 +741,66 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R131530</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AISLACION DE PVC 3M TAPA TRASERA WRM40D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-07-16 14:58:38</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R911041</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MENSULA M-1270</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MENSULA M-1270</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R139650</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PALAS DI-CALL 5 ASPAS Ø 300 C/ BUJE 9.5 MM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PALAS DI-CALL 5 ASPAS Ø 300 C/ BUJE 9.5 MM</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -799,6 +799,146 @@
       </c>
       <c r="D19" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R180309</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MOTOR FLAP MP2835 12V</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:36:52</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>R181561</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BALCON BAMBI LARGO BAJO 51 X12 PROF X 8 ALTO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-17 12:13:04</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R200116</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RELAY EMBRACO CHINO 1/5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RELAY EMBRACO CHINO 1/5</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R222100</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DISYUNTOR 25 A BIPOLAR ZURICH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:49:19</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R470292</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Reduccion 5/16 FH x 1/4 FM de bronce</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reduccion 5/16 FH x 1/4 FM de bronce</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>R472400</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Curvas de cobre p/soldar 3/8 C 180* NAC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Curvas de cobre p/soldar 3/8 C 180* NAC</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R480009</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TF7 4262 F</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-07-20 09:14:29</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/productos_sin_stock.xlsx
+++ b/Backend/productos_sin_stock.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +54,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,25 +443,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="66.140625" customWidth="1" min="2" max="2"/>
+    <col width="20.28515625" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
@@ -452,10 +484,8 @@
           <t>FILTRO PAÑO LAVABLE  X MT2   RE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-13 10:12:23</t>
-        </is>
+      <c r="C2" t="n">
+        <v>0.42</v>
       </c>
       <c r="D2" t="n">
         <v>0.42</v>
@@ -464,78 +494,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R816603</t>
+          <t>R921482</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Termost.RANCO K59L2698 1.05 MTS SE REEMPLA R816606</t>
+          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-13 10:13:23</t>
+          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R907058</t>
+          <t>R937805</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TERMOST. B S  RC94526-2S PATRICK EL FRIO NO SE VA!</t>
-        </is>
+          <t>PALA U. COND. DIAM. 40CM 3 ASPAS BUJE 8MM IZQ.</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R921482</t>
+          <t>R920759</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
+          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tubo recibidor"BlueStar"XF-1.0L---- 1lt-</t>
+          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R937805</t>
+          <t>R965930</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PALA U. COND. DIAM. 40CM 3 ASPAS BUJE 8MM IZQ.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-07-13 16:36:37</t>
-        </is>
+          <t>KIT DE LLAVES ALLEN LARGO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -544,57 +570,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R920759</t>
+          <t>R986608</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
+          <t>Presost.BlueStar HLP530M-Alta 8/30KgManu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LATA GENERICO YH-12 PLUSS 680 GR</t>
+          <t>Presost.BlueStar HLP530M-Alta 8/30KgManu</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R955527</t>
+          <t>R105842</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Termost.RANCO K54L1819  27052 freez WHIR</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-07-14 15:38:02</t>
-        </is>
+          <t>JUEGO DE SUSPENSION COMPLETO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R965930</t>
+          <t>R119279</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KIT DE LLAVES ALLEN LARGO</t>
+          <t>PLAQUETA WHIRPOOL WRE51D1/X1 WRX51D1/X1 326067825</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-15 09:28:38</t>
+          <t>PLAQUETA WHIRPOOL WRE51D1/X1 WRX51D1/X1 326067825</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -604,78 +628,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R986608</t>
+          <t>R119278</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Presost.BlueStar HLP530M-Alta 8/30KgManu</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Presost.BlueStar HLP530M-Alta 8/30KgManu</t>
-        </is>
+          <t>PLAQUETA WHIRPOOL  W10314617  W10165343</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R105842</t>
+          <t>R119364</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JUEGO DE SUSPENSION COMPLETO</t>
+          <t>PLACA REEMPLAZO WH W10165343 / 326053851</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-15 12:04:04</t>
+          <t>PLACA REEMPLAZO WH W10165343 / 326053851</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R119279</t>
+          <t>R119365</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLAQUETA WHIRPOOL WRE51D1/X1 WRX51D1/X1 326067825</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PLAQUETA WHIRPOOL WRE51D1/X1 WRX51D1/X1 326067825</t>
-        </is>
+          <t>PLACA REEMPLAZO WH 326008614</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R119278</t>
+          <t>R119366</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLAQUETA WHIRPOOL  W10314617  W10165343</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-07-15 13:36:12</t>
-        </is>
+          <t>PLACA REEMPLAZO WH 326005413</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -684,57 +702,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R119364</t>
+          <t>R131530</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PLACA REEMPLAZO WH W10165343 / 326053851</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PLACA REEMPLAZO WH W10165343 / 326053851</t>
-        </is>
+          <t>AISLACION DE PVC 3M TAPA TRASERA WRM40D</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R119365</t>
+          <t>R911041</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PLACA REEMPLAZO WH 326008614</t>
+          <t>MENSULA M-1270</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-15 13:46:43</t>
+          <t>MENSULA M-1270</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R119366</t>
+          <t>R139650</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PLACA REEMPLAZO WH 326005413</t>
+          <t>PALAS DI-CALL 5 ASPAS Ø 300 C/ BUJE 9.5 MM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-15 13:46:54</t>
+          <t>PALAS DI-CALL 5 ASPAS Ø 300 C/ BUJE 9.5 MM</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -744,204 +760,137 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R131530</t>
+          <t>R180309</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AISLACION DE PVC 3M TAPA TRASERA WRM40D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-07-16 14:58:38</t>
-        </is>
+          <t>MOTOR FLAP MP2835 12V</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R911041</t>
+          <t>R181561</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MENSULA M-1270</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MENSULA M-1270</t>
-        </is>
+          <t>BALCON BAMBI LARGO BAJO 51 X12 PROF X 8 ALTO</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R139650</t>
+          <t>R200116</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PALAS DI-CALL 5 ASPAS Ø 300 C/ BUJE 9.5 MM</t>
+          <t>RELAY EMBRACO CHINO 1/5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PALAS DI-CALL 5 ASPAS Ø 300 C/ BUJE 9.5 MM</t>
+          <t>RELAY EMBRACO CHINO 1/5</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R180309</t>
+          <t>R222100</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MOTOR FLAP MP2835 12V</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-07-17 10:36:52</t>
-        </is>
+          <t>DISYUNTOR 25 A BIPOLAR ZURICH</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R181561</t>
+          <t>R470292</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BALCON BAMBI LARGO BAJO 51 X12 PROF X 8 ALTO</t>
+          <t>Reduccion 5/16 FH x 1/4 FM de bronce</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-07-17 12:13:04</t>
+          <t>Reduccion 5/16 FH x 1/4 FM de bronce</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R200116</t>
+          <t>R472400</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RELAY EMBRACO CHINO 1/5</t>
+          <t>Curvas de cobre p/soldar 3/8 C 180* NAC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RELAY EMBRACO CHINO 1/5</t>
+          <t>Curvas de cobre p/soldar 3/8 C 180* NAC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R222100</t>
+          <t>R480009</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DISYUNTOR 25 A BIPOLAR ZURICH</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-07-17 15:49:19</t>
-        </is>
+          <t>TF7 4262 F</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>R470292</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Reduccion 5/16 FH x 1/4 FM de bronce</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Reduccion 5/16 FH x 1/4 FM de bronce</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>R472400</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Curvas de cobre p/soldar 3/8 C 180* NAC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Curvas de cobre p/soldar 3/8 C 180* NAC</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>R480009</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>TF7 4262 F</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-07-20 09:14:29</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>